--- a/SECTION SIMULATION STUDIES/Simulation Studies.xlsx
+++ b/SECTION SIMULATION STUDIES/Simulation Studies.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yifan Yang\Desktop\SUB_1 N-MATRICES\Hypothesis Testing Geisser U\UB\VERSION 3.0.0\SECTION SIMULATION STUDIES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yifan Yang\Desktop\SUB_1 N-MATRICES\Hypothesis Testing Geisser U\UB\UB Code VERSION 1.0.0\SECTION SIMULATION STUDIES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{521AF68D-A901-45DA-A691-089AE093DC4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F12D1090-66FD-41A7-8487-A28A9434D188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -328,10 +328,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -637,33 +637,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
+      <c r="E1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
       <c r="E2">
         <v>0.01</v>
       </c>
@@ -687,13 +687,13 @@
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="17">
+      <c r="B3" s="18">
         <v>50</v>
       </c>
-      <c r="C3" s="17">
+      <c r="C3" s="18">
         <v>25</v>
       </c>
       <c r="D3" s="2" t="s">
@@ -722,9 +722,9 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
       <c r="D4" s="2" t="s">
         <v>38</v>
       </c>
@@ -751,9 +751,9 @@
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
       <c r="D5" s="2" t="s">
         <v>39</v>
       </c>
@@ -780,9 +780,9 @@
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
       <c r="D6" s="2" t="s">
         <v>40</v>
       </c>
@@ -809,9 +809,9 @@
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
       <c r="D7" s="2" t="s">
         <v>42</v>
       </c>
@@ -838,9 +838,9 @@
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17">
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18">
         <v>45</v>
       </c>
       <c r="D8" s="2" t="s">
@@ -869,9 +869,9 @@
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
       <c r="D9" s="2" t="s">
         <v>38</v>
       </c>
@@ -898,9 +898,9 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
       <c r="D10" s="2" t="s">
         <v>39</v>
       </c>
@@ -927,9 +927,9 @@
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
       <c r="D11" s="2" t="s">
         <v>40</v>
       </c>
@@ -956,9 +956,9 @@
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
       <c r="D12" s="2" t="s">
         <v>42</v>
       </c>
@@ -985,11 +985,11 @@
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17">
+      <c r="A13" s="18"/>
+      <c r="B13" s="18">
         <v>100</v>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="18">
         <v>75</v>
       </c>
       <c r="D13" s="2" t="s">
@@ -1018,9 +1018,9 @@
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
       <c r="D14" s="2" t="s">
         <v>38</v>
       </c>
@@ -1047,9 +1047,9 @@
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
+      <c r="A15" s="18"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
       <c r="D15" s="2" t="s">
         <v>39</v>
       </c>
@@ -1076,9 +1076,9 @@
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="17"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
+      <c r="A16" s="18"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
       <c r="D16" s="2" t="s">
         <v>40</v>
       </c>
@@ -1105,9 +1105,9 @@
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
       <c r="D17" s="2" t="s">
         <v>42</v>
       </c>
@@ -1134,9 +1134,9 @@
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="17"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17">
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18">
         <v>95</v>
       </c>
       <c r="D18" s="2" t="s">
@@ -1165,9 +1165,9 @@
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="17"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
+      <c r="A19" s="18"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
       <c r="D19" s="2" t="s">
         <v>38</v>
       </c>
@@ -1194,9 +1194,9 @@
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
+      <c r="A20" s="18"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
       <c r="D20" s="2" t="s">
         <v>39</v>
       </c>
@@ -1223,9 +1223,9 @@
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
+      <c r="A21" s="18"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
       <c r="D21" s="2" t="s">
         <v>40</v>
       </c>
@@ -1252,9 +1252,9 @@
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
+      <c r="A22" s="18"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
       <c r="D22" s="2" t="s">
         <v>42</v>
       </c>
@@ -1281,13 +1281,13 @@
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C23" s="17">
+      <c r="C23" s="18">
         <v>200</v>
       </c>
       <c r="D23" s="2" t="s">
@@ -1316,9 +1316,9 @@
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="17"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
+      <c r="A24" s="18"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
       <c r="D24" s="2" t="s">
         <v>40</v>
       </c>
@@ -1345,9 +1345,9 @@
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
+      <c r="A25" s="18"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
       <c r="D25" s="2" t="s">
         <v>42</v>
       </c>
@@ -1374,9 +1374,9 @@
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17">
+      <c r="A26" s="18"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="18">
         <v>400</v>
       </c>
       <c r="D26" s="2" t="s">
@@ -1405,9 +1405,9 @@
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="17"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
+      <c r="A27" s="18"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="18"/>
       <c r="D27" s="2" t="s">
         <v>40</v>
       </c>
@@ -1434,9 +1434,9 @@
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
+      <c r="A28" s="18"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="18"/>
       <c r="D28" s="2" t="s">
         <v>42</v>
       </c>
@@ -1463,11 +1463,11 @@
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="17"/>
-      <c r="B29" s="17" t="s">
+      <c r="A29" s="18"/>
+      <c r="B29" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="17">
+      <c r="C29" s="18">
         <v>200</v>
       </c>
       <c r="D29" s="2" t="s">
@@ -1496,9 +1496,9 @@
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
+      <c r="A30" s="18"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
       <c r="D30" s="2" t="s">
         <v>40</v>
       </c>
@@ -1525,9 +1525,9 @@
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="17"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="18"/>
       <c r="D31" s="2" t="s">
         <v>42</v>
       </c>
@@ -1554,9 +1554,9 @@
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A32" s="17"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17">
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18">
         <v>400</v>
       </c>
       <c r="D32" s="2" t="s">
@@ -1585,9 +1585,9 @@
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A33" s="17"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="18"/>
       <c r="D33" s="2" t="s">
         <v>40</v>
       </c>
@@ -1614,9 +1614,9 @@
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A34" s="17"/>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
+      <c r="A34" s="18"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="18"/>
       <c r="D34" s="2" t="s">
         <v>42</v>
       </c>
@@ -1644,11 +1644,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="E1:K1"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="B23:B28"/>
+    <mergeCell ref="B29:B34"/>
+    <mergeCell ref="A23:A34"/>
+    <mergeCell ref="C23:C25"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="C29:C31"/>
     <mergeCell ref="C3:C7"/>
     <mergeCell ref="C8:C12"/>
     <mergeCell ref="C13:C17"/>
@@ -1656,13 +1658,11 @@
     <mergeCell ref="A3:A22"/>
     <mergeCell ref="B3:B12"/>
     <mergeCell ref="B13:B22"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="B23:B28"/>
-    <mergeCell ref="B29:B34"/>
-    <mergeCell ref="A23:A34"/>
-    <mergeCell ref="C23:C25"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="E1:K1"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -1680,33 +1680,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
+      <c r="E1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
       <c r="E2">
         <v>0.01</v>
       </c>
@@ -1730,13 +1730,13 @@
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="17">
+      <c r="B3" s="18">
         <v>50</v>
       </c>
-      <c r="C3" s="17">
+      <c r="C3" s="18">
         <v>200</v>
       </c>
       <c r="D3" s="2" t="s">
@@ -1765,9 +1765,9 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
       <c r="D4" s="2" t="s">
         <v>44</v>
       </c>
@@ -1794,9 +1794,9 @@
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
       <c r="D5" s="2" t="s">
         <v>40</v>
       </c>
@@ -1823,9 +1823,9 @@
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
       <c r="D6" s="2" t="s">
         <v>42</v>
       </c>
@@ -1852,9 +1852,9 @@
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17">
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18">
         <v>400</v>
       </c>
       <c r="D7" s="2" t="s">
@@ -1883,9 +1883,9 @@
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
       <c r="D8" s="2" t="s">
         <v>44</v>
       </c>
@@ -1912,9 +1912,9 @@
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
       <c r="D9" s="2" t="s">
         <v>40</v>
       </c>
@@ -1941,9 +1941,9 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
       <c r="D10" s="2" t="s">
         <v>42</v>
       </c>
@@ -1970,11 +1970,11 @@
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17">
+      <c r="A11" s="18"/>
+      <c r="B11" s="18">
         <v>100</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="18">
         <v>200</v>
       </c>
       <c r="D11" s="2" t="s">
@@ -2003,9 +2003,9 @@
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
       <c r="D12" s="2" t="s">
         <v>44</v>
       </c>
@@ -2032,9 +2032,9 @@
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
       <c r="D13" s="2" t="s">
         <v>40</v>
       </c>
@@ -2061,9 +2061,9 @@
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
       <c r="D14" s="2" t="s">
         <v>42</v>
       </c>
@@ -2090,9 +2090,9 @@
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17">
+      <c r="A15" s="18"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18">
         <v>400</v>
       </c>
       <c r="D15" s="2" t="s">
@@ -2121,9 +2121,9 @@
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="17"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
+      <c r="A16" s="18"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
       <c r="D16" s="2" t="s">
         <v>44</v>
       </c>
@@ -2150,9 +2150,9 @@
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
       <c r="D17" s="2" t="s">
         <v>40</v>
       </c>
@@ -2179,9 +2179,9 @@
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="17"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
       <c r="D18" s="2" t="s">
         <v>42</v>
       </c>
@@ -2208,13 +2208,13 @@
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B19" s="17">
+      <c r="B19" s="18">
         <v>50</v>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="18">
         <v>200</v>
       </c>
       <c r="D19" s="2" t="s">
@@ -2243,9 +2243,9 @@
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
+      <c r="A20" s="18"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
       <c r="D20" s="2" t="s">
         <v>40</v>
       </c>
@@ -2272,9 +2272,9 @@
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
+      <c r="A21" s="18"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
       <c r="D21" s="2" t="s">
         <v>9</v>
       </c>
@@ -2301,9 +2301,9 @@
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17">
+      <c r="A22" s="18"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18">
         <v>400</v>
       </c>
       <c r="D22" s="2" t="s">
@@ -2332,9 +2332,9 @@
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="17"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
+      <c r="A23" s="18"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
       <c r="D23" s="2" t="s">
         <v>40</v>
       </c>
@@ -2361,9 +2361,9 @@
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="17"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
+      <c r="A24" s="18"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
       <c r="D24" s="2" t="s">
         <v>42</v>
       </c>
@@ -2390,11 +2390,11 @@
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17">
+      <c r="A25" s="18"/>
+      <c r="B25" s="18">
         <v>100</v>
       </c>
-      <c r="C25" s="17">
+      <c r="C25" s="18">
         <v>200</v>
       </c>
       <c r="D25" s="2" t="s">
@@ -2423,9 +2423,9 @@
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
+      <c r="A26" s="18"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="18"/>
       <c r="D26" s="2" t="s">
         <v>40</v>
       </c>
@@ -2452,9 +2452,9 @@
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="17"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
+      <c r="A27" s="18"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="18"/>
       <c r="D27" s="2" t="s">
         <v>42</v>
       </c>
@@ -2481,9 +2481,9 @@
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17">
+      <c r="A28" s="18"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="18">
         <v>400</v>
       </c>
       <c r="D28" s="2" t="s">
@@ -2512,9 +2512,9 @@
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="17"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
+      <c r="A29" s="18"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="18"/>
       <c r="D29" s="2" t="s">
         <v>40</v>
       </c>
@@ -2541,9 +2541,9 @@
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
+      <c r="A30" s="18"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
       <c r="D30" s="2" t="s">
         <v>42</v>
       </c>
@@ -2570,13 +2570,13 @@
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="17" t="s">
+      <c r="A31" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B31" s="17" t="s">
+      <c r="B31" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C31" s="17">
+      <c r="C31" s="18">
         <v>200</v>
       </c>
       <c r="D31" s="2" t="s">
@@ -2605,9 +2605,9 @@
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A32" s="17"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
       <c r="D32" s="2" t="s">
         <v>44</v>
       </c>
@@ -2634,9 +2634,9 @@
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A33" s="17"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="18"/>
       <c r="D33" s="2" t="s">
         <v>40</v>
       </c>
@@ -2663,9 +2663,9 @@
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A34" s="17"/>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
+      <c r="A34" s="18"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="18"/>
       <c r="D34" s="2" t="s">
         <v>42</v>
       </c>
@@ -2692,9 +2692,9 @@
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="17"/>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17">
+      <c r="A35" s="18"/>
+      <c r="B35" s="18"/>
+      <c r="C35" s="18">
         <v>400</v>
       </c>
       <c r="D35" s="2" t="s">
@@ -2723,9 +2723,9 @@
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A36" s="17"/>
-      <c r="B36" s="17"/>
-      <c r="C36" s="17"/>
+      <c r="A36" s="18"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="18"/>
       <c r="D36" s="2" t="s">
         <v>44</v>
       </c>
@@ -2752,9 +2752,9 @@
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A37" s="17"/>
-      <c r="B37" s="17"/>
-      <c r="C37" s="17"/>
+      <c r="A37" s="18"/>
+      <c r="B37" s="18"/>
+      <c r="C37" s="18"/>
       <c r="D37" s="2" t="s">
         <v>40</v>
       </c>
@@ -2781,9 +2781,9 @@
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A38" s="17"/>
-      <c r="B38" s="17"/>
-      <c r="C38" s="17"/>
+      <c r="A38" s="18"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="18"/>
       <c r="D38" s="2" t="s">
         <v>42</v>
       </c>
@@ -2810,11 +2810,11 @@
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A39" s="17"/>
-      <c r="B39" s="17" t="s">
+      <c r="A39" s="18"/>
+      <c r="B39" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C39" s="17">
+      <c r="C39" s="18">
         <v>200</v>
       </c>
       <c r="D39" s="2" t="s">
@@ -2843,9 +2843,9 @@
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A40" s="17"/>
-      <c r="B40" s="17"/>
-      <c r="C40" s="17"/>
+      <c r="A40" s="18"/>
+      <c r="B40" s="18"/>
+      <c r="C40" s="18"/>
       <c r="D40" s="2" t="s">
         <v>44</v>
       </c>
@@ -2872,9 +2872,9 @@
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A41" s="17"/>
-      <c r="B41" s="17"/>
-      <c r="C41" s="17"/>
+      <c r="A41" s="18"/>
+      <c r="B41" s="18"/>
+      <c r="C41" s="18"/>
       <c r="D41" s="2" t="s">
         <v>40</v>
       </c>
@@ -2901,9 +2901,9 @@
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A42" s="17"/>
-      <c r="B42" s="17"/>
-      <c r="C42" s="17"/>
+      <c r="A42" s="18"/>
+      <c r="B42" s="18"/>
+      <c r="C42" s="18"/>
       <c r="D42" s="2" t="s">
         <v>42</v>
       </c>
@@ -2930,9 +2930,9 @@
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A43" s="17"/>
-      <c r="B43" s="17"/>
-      <c r="C43" s="17">
+      <c r="A43" s="18"/>
+      <c r="B43" s="18"/>
+      <c r="C43" s="18">
         <v>400</v>
       </c>
       <c r="D43" s="2" t="s">
@@ -2961,9 +2961,9 @@
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A44" s="17"/>
-      <c r="B44" s="17"/>
-      <c r="C44" s="17"/>
+      <c r="A44" s="18"/>
+      <c r="B44" s="18"/>
+      <c r="C44" s="18"/>
       <c r="D44" s="2" t="s">
         <v>44</v>
       </c>
@@ -2990,9 +2990,9 @@
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A45" s="17"/>
-      <c r="B45" s="17"/>
-      <c r="C45" s="17"/>
+      <c r="A45" s="18"/>
+      <c r="B45" s="18"/>
+      <c r="C45" s="18"/>
       <c r="D45" s="2" t="s">
         <v>40</v>
       </c>
@@ -3019,9 +3019,9 @@
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A46" s="17"/>
-      <c r="B46" s="17"/>
-      <c r="C46" s="17"/>
+      <c r="A46" s="18"/>
+      <c r="B46" s="18"/>
+      <c r="C46" s="18"/>
       <c r="D46" s="2" t="s">
         <v>42</v>
       </c>
@@ -3048,13 +3048,13 @@
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A47" s="17" t="s">
+      <c r="A47" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B47" s="17" t="s">
+      <c r="B47" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C47" s="17">
+      <c r="C47" s="18">
         <v>200</v>
       </c>
       <c r="D47" s="2" t="s">
@@ -3083,9 +3083,9 @@
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A48" s="17"/>
-      <c r="B48" s="17"/>
-      <c r="C48" s="17"/>
+      <c r="A48" s="18"/>
+      <c r="B48" s="18"/>
+      <c r="C48" s="18"/>
       <c r="D48" s="2" t="s">
         <v>45</v>
       </c>
@@ -3112,9 +3112,9 @@
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A49" s="17"/>
-      <c r="B49" s="17"/>
-      <c r="C49" s="17"/>
+      <c r="A49" s="18"/>
+      <c r="B49" s="18"/>
+      <c r="C49" s="18"/>
       <c r="D49" s="2" t="s">
         <v>40</v>
       </c>
@@ -3141,9 +3141,9 @@
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A50" s="17"/>
-      <c r="B50" s="17"/>
-      <c r="C50" s="17"/>
+      <c r="A50" s="18"/>
+      <c r="B50" s="18"/>
+      <c r="C50" s="18"/>
       <c r="D50" s="2" t="s">
         <v>42</v>
       </c>
@@ -3170,9 +3170,9 @@
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A51" s="17"/>
-      <c r="B51" s="17"/>
-      <c r="C51" s="17">
+      <c r="A51" s="18"/>
+      <c r="B51" s="18"/>
+      <c r="C51" s="18">
         <v>400</v>
       </c>
       <c r="D51" s="2" t="s">
@@ -3201,9 +3201,9 @@
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A52" s="17"/>
-      <c r="B52" s="17"/>
-      <c r="C52" s="17"/>
+      <c r="A52" s="18"/>
+      <c r="B52" s="18"/>
+      <c r="C52" s="18"/>
       <c r="D52" s="2" t="s">
         <v>45</v>
       </c>
@@ -3230,9 +3230,9 @@
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A53" s="17"/>
-      <c r="B53" s="17"/>
-      <c r="C53" s="17"/>
+      <c r="A53" s="18"/>
+      <c r="B53" s="18"/>
+      <c r="C53" s="18"/>
       <c r="D53" s="2" t="s">
         <v>40</v>
       </c>
@@ -3259,9 +3259,9 @@
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A54" s="17"/>
-      <c r="B54" s="17"/>
-      <c r="C54" s="17"/>
+      <c r="A54" s="18"/>
+      <c r="B54" s="18"/>
+      <c r="C54" s="18"/>
       <c r="D54" s="2" t="s">
         <v>42</v>
       </c>
@@ -3288,11 +3288,11 @@
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A55" s="17"/>
-      <c r="B55" s="17" t="s">
+      <c r="A55" s="18"/>
+      <c r="B55" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C55" s="17">
+      <c r="C55" s="18">
         <v>200</v>
       </c>
       <c r="D55" s="2" t="s">
@@ -3321,9 +3321,9 @@
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A56" s="17"/>
-      <c r="B56" s="17"/>
-      <c r="C56" s="17"/>
+      <c r="A56" s="18"/>
+      <c r="B56" s="18"/>
+      <c r="C56" s="18"/>
       <c r="D56" s="2" t="s">
         <v>45</v>
       </c>
@@ -3350,9 +3350,9 @@
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A57" s="17"/>
-      <c r="B57" s="17"/>
-      <c r="C57" s="17"/>
+      <c r="A57" s="18"/>
+      <c r="B57" s="18"/>
+      <c r="C57" s="18"/>
       <c r="D57" s="2" t="s">
         <v>40</v>
       </c>
@@ -3379,9 +3379,9 @@
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A58" s="17"/>
-      <c r="B58" s="17"/>
-      <c r="C58" s="17"/>
+      <c r="A58" s="18"/>
+      <c r="B58" s="18"/>
+      <c r="C58" s="18"/>
       <c r="D58" s="2" t="s">
         <v>42</v>
       </c>
@@ -3408,9 +3408,9 @@
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A59" s="17"/>
-      <c r="B59" s="17"/>
-      <c r="C59" s="17">
+      <c r="A59" s="18"/>
+      <c r="B59" s="18"/>
+      <c r="C59" s="18">
         <v>400</v>
       </c>
       <c r="D59" s="2" t="s">
@@ -3439,9 +3439,9 @@
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A60" s="17"/>
-      <c r="B60" s="17"/>
-      <c r="C60" s="17"/>
+      <c r="A60" s="18"/>
+      <c r="B60" s="18"/>
+      <c r="C60" s="18"/>
       <c r="D60" s="2" t="s">
         <v>45</v>
       </c>
@@ -3468,9 +3468,9 @@
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A61" s="17"/>
-      <c r="B61" s="17"/>
-      <c r="C61" s="17"/>
+      <c r="A61" s="18"/>
+      <c r="B61" s="18"/>
+      <c r="C61" s="18"/>
       <c r="D61" s="2" t="s">
         <v>40</v>
       </c>
@@ -3497,9 +3497,9 @@
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A62" s="17"/>
-      <c r="B62" s="17"/>
-      <c r="C62" s="17"/>
+      <c r="A62" s="18"/>
+      <c r="B62" s="18"/>
+      <c r="C62" s="18"/>
       <c r="D62" s="2" t="s">
         <v>42</v>
       </c>
@@ -3527,11 +3527,20 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:K1"/>
+    <mergeCell ref="C59:C62"/>
+    <mergeCell ref="B47:B54"/>
+    <mergeCell ref="B55:B62"/>
+    <mergeCell ref="A47:A62"/>
+    <mergeCell ref="A31:A46"/>
+    <mergeCell ref="C51:C54"/>
+    <mergeCell ref="B31:B38"/>
+    <mergeCell ref="B39:B46"/>
+    <mergeCell ref="C31:C34"/>
+    <mergeCell ref="C35:C38"/>
+    <mergeCell ref="C39:C42"/>
+    <mergeCell ref="C43:C46"/>
+    <mergeCell ref="C47:C50"/>
+    <mergeCell ref="C55:C58"/>
     <mergeCell ref="A19:A30"/>
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="C7:C10"/>
@@ -3546,20 +3555,11 @@
     <mergeCell ref="B19:B24"/>
     <mergeCell ref="C25:C27"/>
     <mergeCell ref="B25:B30"/>
-    <mergeCell ref="C59:C62"/>
-    <mergeCell ref="B47:B54"/>
-    <mergeCell ref="B55:B62"/>
-    <mergeCell ref="A47:A62"/>
-    <mergeCell ref="A31:A46"/>
-    <mergeCell ref="C51:C54"/>
-    <mergeCell ref="B31:B38"/>
-    <mergeCell ref="B39:B46"/>
-    <mergeCell ref="C31:C34"/>
-    <mergeCell ref="C35:C38"/>
-    <mergeCell ref="C39:C42"/>
-    <mergeCell ref="C43:C46"/>
-    <mergeCell ref="C47:C50"/>
-    <mergeCell ref="C55:C58"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:K1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3577,10 +3577,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="18" t="s">
         <v>54</v>
       </c>
       <c r="C1" s="19" t="s">
@@ -3612,49 +3612,49 @@
       <c r="U1" s="22"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
       <c r="C2" s="19"/>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18" t="s">
+      <c r="E2" s="17"/>
+      <c r="F2" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18" t="s">
+      <c r="G2" s="17"/>
+      <c r="H2" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18" t="s">
+      <c r="I2" s="17"/>
+      <c r="J2" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18" t="s">
+      <c r="K2" s="17"/>
+      <c r="L2" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="18"/>
-      <c r="N2" s="18" t="s">
+      <c r="M2" s="17"/>
+      <c r="N2" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="18"/>
-      <c r="P2" s="18" t="s">
+      <c r="O2" s="17"/>
+      <c r="P2" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="Q2" s="18"/>
-      <c r="R2" s="18" t="s">
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="S2" s="18"/>
-      <c r="T2" s="18" t="s">
+      <c r="S2" s="17"/>
+      <c r="T2" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="U2" s="18"/>
+      <c r="U2" s="17"/>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
       <c r="C3" s="19"/>
       <c r="D3" s="3" t="s">
         <v>16</v>
@@ -74599,131 +74599,131 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18" t="s">
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
-      <c r="P1" s="18"/>
-      <c r="Q1" s="18"/>
-      <c r="R1" s="18"/>
-      <c r="S1" s="18"/>
-      <c r="T1" s="18"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="17"/>
+      <c r="S1" s="17"/>
+      <c r="T1" s="17"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="17" t="s">
+      <c r="V1" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="W1" s="17" t="s">
+      <c r="W1" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="X1" s="18" t="s">
+      <c r="X1" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="18"/>
-      <c r="Z1" s="18"/>
-      <c r="AA1" s="18"/>
-      <c r="AB1" s="18" t="s">
+      <c r="Y1" s="17"/>
+      <c r="Z1" s="17"/>
+      <c r="AA1" s="17"/>
+      <c r="AB1" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="AC1" s="18"/>
-      <c r="AD1" s="18"/>
-      <c r="AE1" s="18"/>
+      <c r="AC1" s="17"/>
+      <c r="AD1" s="17"/>
+      <c r="AE1" s="17"/>
       <c r="AF1" s="1"/>
-      <c r="AG1" s="17" t="s">
+      <c r="AG1" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="AH1" s="17" t="s">
+      <c r="AH1" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="AI1" s="18" t="s">
+      <c r="AI1" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="AJ1" s="18"/>
-      <c r="AK1" s="18"/>
-      <c r="AL1" s="18"/>
-      <c r="AM1" s="18"/>
-      <c r="AN1" s="18"/>
-      <c r="AO1" s="18"/>
-      <c r="AP1" s="18"/>
-      <c r="AQ1" s="18"/>
-      <c r="AR1" s="18"/>
-      <c r="AS1" s="18"/>
-      <c r="AT1" s="18"/>
-      <c r="AU1" s="18"/>
-      <c r="AV1" s="18"/>
-      <c r="AW1" s="18"/>
-      <c r="AX1" s="18" t="s">
+      <c r="AJ1" s="17"/>
+      <c r="AK1" s="17"/>
+      <c r="AL1" s="17"/>
+      <c r="AM1" s="17"/>
+      <c r="AN1" s="17"/>
+      <c r="AO1" s="17"/>
+      <c r="AP1" s="17"/>
+      <c r="AQ1" s="17"/>
+      <c r="AR1" s="17"/>
+      <c r="AS1" s="17"/>
+      <c r="AT1" s="17"/>
+      <c r="AU1" s="17"/>
+      <c r="AV1" s="17"/>
+      <c r="AW1" s="17"/>
+      <c r="AX1" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="AY1" s="18"/>
-      <c r="AZ1" s="18"/>
-      <c r="BA1" s="18"/>
-      <c r="BB1" s="18"/>
-      <c r="BC1" s="18"/>
-      <c r="BD1" s="18"/>
-      <c r="BE1" s="18"/>
-      <c r="BF1" s="18"/>
-      <c r="BG1" s="18"/>
-      <c r="BH1" s="18"/>
-      <c r="BI1" s="18"/>
-      <c r="BJ1" s="18"/>
-      <c r="BK1" s="18"/>
-      <c r="BL1" s="18"/>
+      <c r="AY1" s="17"/>
+      <c r="AZ1" s="17"/>
+      <c r="BA1" s="17"/>
+      <c r="BB1" s="17"/>
+      <c r="BC1" s="17"/>
+      <c r="BD1" s="17"/>
+      <c r="BE1" s="17"/>
+      <c r="BF1" s="17"/>
+      <c r="BG1" s="17"/>
+      <c r="BH1" s="17"/>
+      <c r="BI1" s="17"/>
+      <c r="BJ1" s="17"/>
+      <c r="BK1" s="17"/>
+      <c r="BL1" s="17"/>
     </row>
     <row r="2" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="18" t="s">
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18" t="s">
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18" t="s">
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18" t="s">
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="18"/>
-      <c r="N2" s="18"/>
-      <c r="O2" s="18" t="s">
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="P2" s="18"/>
-      <c r="Q2" s="18"/>
-      <c r="R2" s="18" t="s">
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="S2" s="18"/>
-      <c r="T2" s="18"/>
+      <c r="S2" s="17"/>
+      <c r="T2" s="17"/>
       <c r="U2" s="1"/>
-      <c r="V2" s="17"/>
-      <c r="W2" s="17"/>
+      <c r="V2" s="18"/>
+      <c r="W2" s="18"/>
       <c r="X2" s="1" t="s">
         <v>28</v>
       </c>
@@ -74749,8 +74749,8 @@
         <v>31</v>
       </c>
       <c r="AF2" s="1"/>
-      <c r="AG2" s="17"/>
-      <c r="AH2" s="17"/>
+      <c r="AG2" s="18"/>
+      <c r="AH2" s="18"/>
       <c r="AI2" s="1" t="s">
         <v>57</v>
       </c>
@@ -74843,8 +74843,8 @@
       </c>
     </row>
     <row r="3" spans="1:64" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
       <c r="C3" s="8" t="s">
         <v>46</v>
       </c>
@@ -74899,67 +74899,67 @@
       <c r="T3" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="V3" s="17"/>
-      <c r="W3" s="17"/>
-      <c r="X3" s="17" t="s">
+      <c r="V3" s="18"/>
+      <c r="W3" s="18"/>
+      <c r="X3" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="Y3" s="17"/>
-      <c r="Z3" s="17"/>
-      <c r="AA3" s="17"/>
-      <c r="AB3" s="17" t="s">
+      <c r="Y3" s="18"/>
+      <c r="Z3" s="18"/>
+      <c r="AA3" s="18"/>
+      <c r="AB3" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="AC3" s="17"/>
-      <c r="AD3" s="17"/>
-      <c r="AE3" s="17"/>
-      <c r="AG3" s="17"/>
-      <c r="AH3" s="17"/>
-      <c r="AI3" s="17" t="s">
+      <c r="AC3" s="18"/>
+      <c r="AD3" s="18"/>
+      <c r="AE3" s="18"/>
+      <c r="AG3" s="18"/>
+      <c r="AH3" s="18"/>
+      <c r="AI3" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="AJ3" s="17"/>
-      <c r="AK3" s="17"/>
-      <c r="AL3" s="17"/>
-      <c r="AM3" s="17"/>
-      <c r="AN3" s="17" t="s">
+      <c r="AJ3" s="18"/>
+      <c r="AK3" s="18"/>
+      <c r="AL3" s="18"/>
+      <c r="AM3" s="18"/>
+      <c r="AN3" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="AO3" s="17"/>
-      <c r="AP3" s="17"/>
-      <c r="AQ3" s="17"/>
-      <c r="AR3" s="17"/>
-      <c r="AS3" s="17" t="s">
+      <c r="AO3" s="18"/>
+      <c r="AP3" s="18"/>
+      <c r="AQ3" s="18"/>
+      <c r="AR3" s="18"/>
+      <c r="AS3" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="AT3" s="17"/>
-      <c r="AU3" s="17"/>
-      <c r="AV3" s="17"/>
-      <c r="AW3" s="17"/>
-      <c r="AX3" s="17" t="s">
+      <c r="AT3" s="18"/>
+      <c r="AU3" s="18"/>
+      <c r="AV3" s="18"/>
+      <c r="AW3" s="18"/>
+      <c r="AX3" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="AY3" s="17"/>
-      <c r="AZ3" s="17"/>
-      <c r="BA3" s="17"/>
-      <c r="BB3" s="17"/>
-      <c r="BC3" s="17" t="s">
+      <c r="AY3" s="18"/>
+      <c r="AZ3" s="18"/>
+      <c r="BA3" s="18"/>
+      <c r="BB3" s="18"/>
+      <c r="BC3" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="BD3" s="17"/>
-      <c r="BE3" s="17"/>
-      <c r="BF3" s="17"/>
-      <c r="BG3" s="17"/>
-      <c r="BH3" s="17" t="s">
+      <c r="BD3" s="18"/>
+      <c r="BE3" s="18"/>
+      <c r="BF3" s="18"/>
+      <c r="BG3" s="18"/>
+      <c r="BH3" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="BI3" s="17"/>
-      <c r="BJ3" s="17"/>
-      <c r="BK3" s="17"/>
-      <c r="BL3" s="17"/>
+      <c r="BI3" s="18"/>
+      <c r="BJ3" s="18"/>
+      <c r="BK3" s="18"/>
+      <c r="BL3" s="18"/>
     </row>
     <row r="4" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="17" t="s">
         <v>34</v>
       </c>
       <c r="B4">
@@ -75020,7 +75020,7 @@
         <v>0.156</v>
       </c>
       <c r="U4" s="4"/>
-      <c r="V4" s="18" t="s">
+      <c r="V4" s="17" t="s">
         <v>34</v>
       </c>
       <c r="W4" s="1">
@@ -75051,7 +75051,7 @@
         <v>0.28399999999999997</v>
       </c>
       <c r="AF4" s="15"/>
-      <c r="AG4" s="18" t="s">
+      <c r="AG4" s="17" t="s">
         <v>34</v>
       </c>
       <c r="AH4" s="1">
@@ -75149,7 +75149,7 @@
       </c>
     </row>
     <row r="5" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A5" s="18"/>
+      <c r="A5" s="17"/>
       <c r="B5" s="5">
         <v>0.1</v>
       </c>
@@ -75208,7 +75208,7 @@
         <v>0.19700000000000001</v>
       </c>
       <c r="U5" s="4"/>
-      <c r="V5" s="18"/>
+      <c r="V5" s="17"/>
       <c r="W5" s="16">
         <v>0.1</v>
       </c>
@@ -75237,7 +75237,7 @@
         <v>1</v>
       </c>
       <c r="AF5" s="15"/>
-      <c r="AG5" s="18"/>
+      <c r="AG5" s="17"/>
       <c r="AH5" s="16">
         <v>0.1</v>
       </c>
@@ -75333,7 +75333,7 @@
       </c>
     </row>
     <row r="6" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A6" s="18"/>
+      <c r="A6" s="17"/>
       <c r="B6" s="5">
         <v>0.2</v>
       </c>
@@ -75392,7 +75392,7 @@
         <v>0.20200000000000001</v>
       </c>
       <c r="U6" s="4"/>
-      <c r="V6" s="18"/>
+      <c r="V6" s="17"/>
       <c r="W6" s="16">
         <v>0.2</v>
       </c>
@@ -75421,7 +75421,7 @@
         <v>1</v>
       </c>
       <c r="AF6" s="15"/>
-      <c r="AG6" s="18"/>
+      <c r="AG6" s="17"/>
       <c r="AH6" s="16">
         <v>0.2</v>
       </c>
@@ -75517,7 +75517,7 @@
       </c>
     </row>
     <row r="7" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A7" s="18"/>
+      <c r="A7" s="17"/>
       <c r="B7" s="5">
         <v>0.5</v>
       </c>
@@ -75576,7 +75576,7 @@
         <v>0.17299999999999999</v>
       </c>
       <c r="U7" s="4"/>
-      <c r="V7" s="18"/>
+      <c r="V7" s="17"/>
       <c r="W7" s="16">
         <v>0.5</v>
       </c>
@@ -75605,7 +75605,7 @@
         <v>1</v>
       </c>
       <c r="AF7" s="15"/>
-      <c r="AG7" s="18"/>
+      <c r="AG7" s="17"/>
       <c r="AH7" s="16">
         <v>0.5</v>
       </c>
@@ -75701,7 +75701,7 @@
       </c>
     </row>
     <row r="8" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A8" s="18"/>
+      <c r="A8" s="17"/>
       <c r="B8" s="5">
         <v>0.8</v>
       </c>
@@ -75760,7 +75760,7 @@
         <v>0.44</v>
       </c>
       <c r="U8" s="4"/>
-      <c r="V8" s="18"/>
+      <c r="V8" s="17"/>
       <c r="W8" s="16">
         <v>0.8</v>
       </c>
@@ -75789,7 +75789,7 @@
         <v>1</v>
       </c>
       <c r="AF8" s="15"/>
-      <c r="AG8" s="18"/>
+      <c r="AG8" s="17"/>
       <c r="AH8" s="16">
         <v>0.8</v>
       </c>
@@ -75885,7 +75885,7 @@
       </c>
     </row>
     <row r="9" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A9" s="18"/>
+      <c r="A9" s="17"/>
       <c r="B9" s="5">
         <v>0.9</v>
       </c>
@@ -75944,7 +75944,7 @@
         <v>0.34799999999999998</v>
       </c>
       <c r="U9" s="4"/>
-      <c r="V9" s="18"/>
+      <c r="V9" s="17"/>
       <c r="W9" s="16">
         <v>0.9</v>
       </c>
@@ -75973,7 +75973,7 @@
         <v>1</v>
       </c>
       <c r="AF9" s="15"/>
-      <c r="AG9" s="18"/>
+      <c r="AG9" s="17"/>
       <c r="AH9" s="16">
         <v>0.9</v>
       </c>
@@ -76069,7 +76069,7 @@
       </c>
     </row>
     <row r="10" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A10" s="18"/>
+      <c r="A10" s="17"/>
       <c r="B10" s="5">
         <v>1</v>
       </c>
@@ -76128,7 +76128,7 @@
         <v>0.111</v>
       </c>
       <c r="U10" s="4"/>
-      <c r="V10" s="18"/>
+      <c r="V10" s="17"/>
       <c r="W10" s="16">
         <v>1</v>
       </c>
@@ -76157,7 +76157,7 @@
         <v>0.157</v>
       </c>
       <c r="AF10" s="15"/>
-      <c r="AG10" s="18"/>
+      <c r="AG10" s="17"/>
       <c r="AH10" s="16">
         <v>1</v>
       </c>
@@ -76253,7 +76253,7 @@
       </c>
     </row>
     <row r="11" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="17" t="s">
         <v>35</v>
       </c>
       <c r="B11">
@@ -76314,7 +76314,7 @@
         <v>0.20599999999999999</v>
       </c>
       <c r="U11" s="4"/>
-      <c r="V11" s="18" t="s">
+      <c r="V11" s="17" t="s">
         <v>35</v>
       </c>
       <c r="W11" s="1">
@@ -76345,7 +76345,7 @@
         <v>0.99099999999999999</v>
       </c>
       <c r="AF11" s="15"/>
-      <c r="AG11" s="18" t="s">
+      <c r="AG11" s="17" t="s">
         <v>35</v>
       </c>
       <c r="AH11" s="1">
@@ -76443,7 +76443,7 @@
       </c>
     </row>
     <row r="12" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A12" s="18"/>
+      <c r="A12" s="17"/>
       <c r="B12" s="5">
         <v>0.1</v>
       </c>
@@ -76502,7 +76502,7 @@
         <v>0.316</v>
       </c>
       <c r="U12" s="4"/>
-      <c r="V12" s="18"/>
+      <c r="V12" s="17"/>
       <c r="W12" s="16">
         <v>0.1</v>
       </c>
@@ -76531,7 +76531,7 @@
         <v>1</v>
       </c>
       <c r="AF12" s="15"/>
-      <c r="AG12" s="18"/>
+      <c r="AG12" s="17"/>
       <c r="AH12" s="16">
         <v>0.1</v>
       </c>
@@ -76627,7 +76627,7 @@
       </c>
     </row>
     <row r="13" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A13" s="18"/>
+      <c r="A13" s="17"/>
       <c r="B13" s="5">
         <v>0.2</v>
       </c>
@@ -76686,7 +76686,7 @@
         <v>0.33</v>
       </c>
       <c r="U13" s="4"/>
-      <c r="V13" s="18"/>
+      <c r="V13" s="17"/>
       <c r="W13" s="16">
         <v>0.2</v>
       </c>
@@ -76715,7 +76715,7 @@
         <v>1</v>
       </c>
       <c r="AF13" s="15"/>
-      <c r="AG13" s="18"/>
+      <c r="AG13" s="17"/>
       <c r="AH13" s="16">
         <v>0.2</v>
       </c>
@@ -76811,7 +76811,7 @@
       </c>
     </row>
     <row r="14" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A14" s="18"/>
+      <c r="A14" s="17"/>
       <c r="B14" s="5">
         <v>0.5</v>
       </c>
@@ -76870,7 +76870,7 @@
         <v>0.27800000000000002</v>
       </c>
       <c r="U14" s="4"/>
-      <c r="V14" s="18"/>
+      <c r="V14" s="17"/>
       <c r="W14" s="16">
         <v>0.5</v>
       </c>
@@ -76899,7 +76899,7 @@
         <v>1</v>
       </c>
       <c r="AF14" s="15"/>
-      <c r="AG14" s="18"/>
+      <c r="AG14" s="17"/>
       <c r="AH14" s="16">
         <v>0.5</v>
       </c>
@@ -76995,7 +76995,7 @@
       </c>
     </row>
     <row r="15" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A15" s="18"/>
+      <c r="A15" s="17"/>
       <c r="B15" s="5">
         <v>0.8</v>
       </c>
@@ -77054,7 +77054,7 @@
         <v>0.64800000000000002</v>
       </c>
       <c r="U15" s="4"/>
-      <c r="V15" s="18"/>
+      <c r="V15" s="17"/>
       <c r="W15" s="16">
         <v>0.8</v>
       </c>
@@ -77083,7 +77083,7 @@
         <v>1</v>
       </c>
       <c r="AF15" s="15"/>
-      <c r="AG15" s="18"/>
+      <c r="AG15" s="17"/>
       <c r="AH15" s="16">
         <v>0.8</v>
       </c>
@@ -77179,7 +77179,7 @@
       </c>
     </row>
     <row r="16" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A16" s="18"/>
+      <c r="A16" s="17"/>
       <c r="B16" s="5">
         <v>0.9</v>
       </c>
@@ -77238,7 +77238,7 @@
         <v>0.45700000000000002</v>
       </c>
       <c r="U16" s="4"/>
-      <c r="V16" s="18"/>
+      <c r="V16" s="17"/>
       <c r="W16" s="16">
         <v>0.9</v>
       </c>
@@ -77267,7 +77267,7 @@
         <v>1</v>
       </c>
       <c r="AF16" s="15"/>
-      <c r="AG16" s="18"/>
+      <c r="AG16" s="17"/>
       <c r="AH16" s="16">
         <v>0.9</v>
       </c>
@@ -77363,7 +77363,7 @@
       </c>
     </row>
     <row r="17" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A17" s="18"/>
+      <c r="A17" s="17"/>
       <c r="B17" s="5">
         <v>1</v>
       </c>
@@ -77422,7 +77422,7 @@
         <v>0.111</v>
       </c>
       <c r="U17" s="4"/>
-      <c r="V17" s="18"/>
+      <c r="V17" s="17"/>
       <c r="W17" s="16">
         <v>1</v>
       </c>
@@ -77451,7 +77451,7 @@
         <v>0.157</v>
       </c>
       <c r="AF17" s="15"/>
-      <c r="AG17" s="18"/>
+      <c r="AG17" s="17"/>
       <c r="AH17" s="16">
         <v>1</v>
       </c>
@@ -77547,7 +77547,7 @@
       </c>
     </row>
     <row r="18" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="17" t="s">
         <v>36</v>
       </c>
       <c r="B18">
@@ -77608,7 +77608,7 @@
         <v>0.20399999999999999</v>
       </c>
       <c r="U18" s="4"/>
-      <c r="V18" s="18" t="s">
+      <c r="V18" s="17" t="s">
         <v>36</v>
       </c>
       <c r="W18" s="1">
@@ -77639,7 +77639,7 @@
         <v>0.99199999999999999</v>
       </c>
       <c r="AF18" s="15"/>
-      <c r="AG18" s="18" t="s">
+      <c r="AG18" s="17" t="s">
         <v>36</v>
       </c>
       <c r="AH18" s="1">
@@ -77737,7 +77737,7 @@
       </c>
     </row>
     <row r="19" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A19" s="18"/>
+      <c r="A19" s="17"/>
       <c r="B19" s="5">
         <v>0.1</v>
       </c>
@@ -77796,7 +77796,7 @@
         <v>0.318</v>
       </c>
       <c r="U19" s="4"/>
-      <c r="V19" s="18"/>
+      <c r="V19" s="17"/>
       <c r="W19" s="16">
         <v>0.1</v>
       </c>
@@ -77825,7 +77825,7 @@
         <v>1</v>
       </c>
       <c r="AF19" s="15"/>
-      <c r="AG19" s="18"/>
+      <c r="AG19" s="17"/>
       <c r="AH19" s="16">
         <v>0.1</v>
       </c>
@@ -77921,7 +77921,7 @@
       </c>
     </row>
     <row r="20" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A20" s="18"/>
+      <c r="A20" s="17"/>
       <c r="B20" s="5">
         <v>0.2</v>
       </c>
@@ -77980,7 +77980,7 @@
         <v>0.33800000000000002</v>
       </c>
       <c r="U20" s="4"/>
-      <c r="V20" s="18"/>
+      <c r="V20" s="17"/>
       <c r="W20" s="16">
         <v>0.2</v>
       </c>
@@ -78009,7 +78009,7 @@
         <v>1</v>
       </c>
       <c r="AF20" s="15"/>
-      <c r="AG20" s="18"/>
+      <c r="AG20" s="17"/>
       <c r="AH20" s="16">
         <v>0.2</v>
       </c>
@@ -78105,7 +78105,7 @@
       </c>
     </row>
     <row r="21" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A21" s="18"/>
+      <c r="A21" s="17"/>
       <c r="B21" s="5">
         <v>0.5</v>
       </c>
@@ -78164,7 +78164,7 @@
         <v>0.26700000000000002</v>
       </c>
       <c r="U21" s="4"/>
-      <c r="V21" s="18"/>
+      <c r="V21" s="17"/>
       <c r="W21" s="16">
         <v>0.5</v>
       </c>
@@ -78193,7 +78193,7 @@
         <v>1</v>
       </c>
       <c r="AF21" s="15"/>
-      <c r="AG21" s="18"/>
+      <c r="AG21" s="17"/>
       <c r="AH21" s="16">
         <v>0.5</v>
       </c>
@@ -78289,7 +78289,7 @@
       </c>
     </row>
     <row r="22" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A22" s="18"/>
+      <c r="A22" s="17"/>
       <c r="B22" s="5">
         <v>0.8</v>
       </c>
@@ -78348,7 +78348,7 @@
         <v>0.64700000000000002</v>
       </c>
       <c r="U22" s="4"/>
-      <c r="V22" s="18"/>
+      <c r="V22" s="17"/>
       <c r="W22" s="16">
         <v>0.8</v>
       </c>
@@ -78377,7 +78377,7 @@
         <v>1</v>
       </c>
       <c r="AF22" s="15"/>
-      <c r="AG22" s="18"/>
+      <c r="AG22" s="17"/>
       <c r="AH22" s="16">
         <v>0.8</v>
       </c>
@@ -78473,7 +78473,7 @@
       </c>
     </row>
     <row r="23" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A23" s="18"/>
+      <c r="A23" s="17"/>
       <c r="B23" s="5">
         <v>0.9</v>
       </c>
@@ -78532,7 +78532,7 @@
         <v>0.45700000000000002</v>
       </c>
       <c r="U23" s="4"/>
-      <c r="V23" s="18"/>
+      <c r="V23" s="17"/>
       <c r="W23" s="16">
         <v>0.9</v>
       </c>
@@ -78561,7 +78561,7 @@
         <v>1</v>
       </c>
       <c r="AF23" s="15"/>
-      <c r="AG23" s="18"/>
+      <c r="AG23" s="17"/>
       <c r="AH23" s="16">
         <v>0.9</v>
       </c>
@@ -78657,7 +78657,7 @@
       </c>
     </row>
     <row r="24" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A24" s="18"/>
+      <c r="A24" s="17"/>
       <c r="B24" s="5">
         <v>1</v>
       </c>
@@ -78716,7 +78716,7 @@
         <v>0.111</v>
       </c>
       <c r="U24" s="4"/>
-      <c r="V24" s="18"/>
+      <c r="V24" s="17"/>
       <c r="W24" s="16">
         <v>1</v>
       </c>
@@ -78745,7 +78745,7 @@
         <v>0.157</v>
       </c>
       <c r="AF24" s="15"/>
-      <c r="AG24" s="18"/>
+      <c r="AG24" s="17"/>
       <c r="AH24" s="16">
         <v>1</v>
       </c>
@@ -78842,20 +78842,11 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="A4:A10"/>
-    <mergeCell ref="A11:A17"/>
-    <mergeCell ref="A18:A24"/>
-    <mergeCell ref="X1:AA1"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="C1:K1"/>
-    <mergeCell ref="L1:T1"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="V4:V10"/>
-    <mergeCell ref="V11:V17"/>
+    <mergeCell ref="AG1:AG3"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="V1:V3"/>
+    <mergeCell ref="W1:W3"/>
     <mergeCell ref="BH3:BL3"/>
     <mergeCell ref="AX1:BL1"/>
     <mergeCell ref="AI1:AW1"/>
@@ -78872,11 +78863,20 @@
     <mergeCell ref="AS3:AW3"/>
     <mergeCell ref="AB1:AE1"/>
     <mergeCell ref="AB3:AE3"/>
-    <mergeCell ref="AG1:AG3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="V1:V3"/>
-    <mergeCell ref="W1:W3"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="A11:A17"/>
+    <mergeCell ref="A18:A24"/>
+    <mergeCell ref="X1:AA1"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="C1:K1"/>
+    <mergeCell ref="L1:T1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="V4:V10"/>
+    <mergeCell ref="V11:V17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
